--- a/Excel/BabelConfig.xlsx
+++ b/Excel/BabelConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -159,6 +159,24 @@
   </si>
   <si>
     <t>7000,500,1,1</t>
+  </si>
+  <si>
+    <t>5001,5002,16,5003</t>
+  </si>
+  <si>
+    <t>10000,600,1,1</t>
+  </si>
+  <si>
+    <t>15000,700,1,1</t>
+  </si>
+  <si>
+    <t>20000,800,1,1</t>
+  </si>
+  <si>
+    <t>25000,900,1,1</t>
+  </si>
+  <si>
+    <t>30000,1000,1,1</t>
   </si>
 </sst>
 </file>
@@ -341,12 +359,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1135,7 +1153,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1295,7 +1313,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" ref="D7:D15" si="0">E6+1</f>
+        <f t="shared" ref="D7:D21" si="0">E6+1</f>
         <v>201</v>
       </c>
       <c r="E7" s="1">
@@ -1533,103 +1551,223 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1"/>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="6:9">
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="6:9">
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <f>E15+1</f>
+        <v>2001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2200</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <f>E16+1</f>
+        <v>2201</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2400</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1">
+        <f>E17+1</f>
+        <v>2401</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2600</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <f>E18+1</f>
+        <v>2601</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2800</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <f>E19+1</f>
+        <v>2801</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1"/>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F22" s="5"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F23" s="5"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F24" s="5"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F25" s="5"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F26" s="5"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="F27" s="5"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="6:9">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="F28" s="5"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="6:9">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:10">
       <c r="F29" s="5"/>
-    </row>
-    <row r="30" customHeight="1" spans="6:9">
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:10">
       <c r="F30" s="5"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" customHeight="1" spans="6:9">
+    <row r="31" customHeight="1" spans="3:10">
       <c r="F31" s="5"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" customHeight="1" spans="6:9">
-      <c r="F32" s="5"/>
-      <c r="G32" s="1"/>
+    <row r="32" customHeight="1" spans="3:10">
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="6:9">
-      <c r="F33" s="5"/>
-      <c r="G33" s="1"/>
+    <row r="33" customHeight="1" spans="8:9">
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="6:9">
+    <row r="34" customHeight="1" spans="8:9">
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="6:9">
+    <row r="35" customHeight="1" spans="8:9">
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="6:9">
+    <row r="36" customHeight="1" spans="8:9">
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="6:9">
+    <row r="37" customHeight="1" spans="8:9">
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="6:9">
+    <row r="38" customHeight="1" spans="8:9">
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="6:9">
+    <row r="39" customHeight="1" spans="8:9">
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="6:9">
+    <row r="40" customHeight="1" spans="8:9">
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="6:9">
+    <row r="41" customHeight="1" spans="8:9">
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="6:9">
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="6:9">
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
